--- a/nr-update-valueset/ig/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/nr-update-valueset/ig/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T14:32:05+00:00</t>
+    <t>2024-03-06T16:49:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Contact</t>

--- a/nr-update-valueset/ig/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/nr-update-valueset/ig/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$78</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3328" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2862" uniqueCount="491">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T16:49:12+00:00</t>
+    <t>2024-03-07T12:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -647,13 +647,10 @@
 </t>
   </si>
   <si>
-    <t>Secteur de conventionnement du professionnel libéral auquel il a adhéré auprès de l'Assurance Maladie.</t>
+    <t>Secteur de conventionnement du professionnel libéral auquel il a adhéré auprès de l'Assurance Maladie (Synonyme : secteurConventionnement).</t>
   </si>
   <si>
     <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire le secteur de conventionnement du professionnel libéral auquel il a adhéré auprès de l'Assurance Maladie.</t>
-  </si>
-  <si>
-    <t>Synonyme : secteurConventionnement</t>
   </si>
   <si>
     <t>PractitionerRole.extension:as-ext-practitionerrole-hascas</t>
@@ -1385,256 +1382,6 @@
     <t>TEL</t>
   </si>
   <si>
-    <t>PractitionerRole.telecom:mailbox-mss.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:emailType</t>
-  </si>
-  <si>
-    <t>emailType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://interopsante.org/fhir/StructureDefinition/FrContactPointEmailType}
-</t>
-  </si>
-  <si>
-    <t>Type of email | type de messagerie électronique</t>
-  </si>
-  <si>
-    <t>Optional Extension Element - found in all resources.</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:emailType.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.extension.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:emailType.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.extension.extension</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:emailType.url</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.extension.url</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>http://interopsante.org/fhir/StructureDefinition/FrContactPointEmailType</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:emailType.value[x]</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.extension.value[x]</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="https://mos.esante.gouv.fr/NOS/TRE_R256-TypeMessagerie/FHIR/TRE-R256-TypeMessagerie"/&gt;
-  &lt;code value="MSSANTE"/&gt;
-&lt;/valueCoding&gt;</t>
-  </si>
-  <si>
-    <t>http://interopsante.org/fhir/ValueSet/fr-email-type</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata</t>
-  </si>
-  <si>
-    <t>as-mailbox-mss-metadata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata}
-</t>
-  </si>
-  <si>
-    <t>Les attributs 'responsible' et 'phone' ne sont pas disponibles en accès libre.</t>
-  </si>
-  <si>
-    <t>Extension contenant les métadonnées de la mailbox mss.</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.system</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.system</t>
-  </si>
-  <si>
-    <t>phone | fax | email | pager | url | sms | other</t>
-  </si>
-  <si>
-    <t>Telecommunications form for contact point - what communications system is required to make use of the contact.</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>Telecommunications form for contact point.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/contact-point-system</t>
-  </si>
-  <si>
-    <t>ContactPoint.system</t>
-  </si>
-  <si>
-    <t>ele-1
-cpt-2</t>
-  </si>
-  <si>
-    <t>XTN.3</t>
-  </si>
-  <si>
-    <t>./scheme</t>
-  </si>
-  <si>
-    <t>./ContactPointType</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.value</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.value</t>
-  </si>
-  <si>
-    <t>Boîte Aux Lettres (BAL) MSS</t>
-  </si>
-  <si>
-    <t>The actual contact point details, in a form that is meaningful to the designated communication system (i.e. phone number or email address).</t>
-  </si>
-  <si>
-    <t>Additional text data such as phone extension numbers, or notes about use of the contact are sometimes included in the value.</t>
-  </si>
-  <si>
-    <t>Need to support legacy numbers that are not in a tightly controlled format.</t>
-  </si>
-  <si>
-    <t>ContactPoint.value</t>
-  </si>
-  <si>
-    <t>XTN.1 (or XTN.12)</t>
-  </si>
-  <si>
-    <t>./url</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.use</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.use</t>
-  </si>
-  <si>
-    <t>home | work | temp | old | mobile - purpose of this contact point</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for the contact point.</t>
-  </si>
-  <si>
-    <t>Applications can assume that a contact is current unless it explicitly says that it is temporary or old.</t>
-  </si>
-  <si>
-    <t>Need to track the way a person uses this contact, so a user can choose which is appropriate for their purpose.</t>
-  </si>
-  <si>
-    <t>Use of contact point.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/contact-point-use</t>
-  </si>
-  <si>
-    <t>ContactPoint.use</t>
-  </si>
-  <si>
-    <t>XTN.2 - but often indicated by field</t>
-  </si>
-  <si>
-    <t>unique(./use)</t>
-  </si>
-  <si>
-    <t>./ContactPointPurpose</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.rank</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">positiveInt
-</t>
-  </si>
-  <si>
-    <t>Specify preferred order of use (1 = highest)</t>
-  </si>
-  <si>
-    <t>Specifies a preferred order in which to use a set of contacts. ContactPoints with lower rank values are more preferred than those with higher rank values.</t>
-  </si>
-  <si>
-    <t>Note that rank does not necessarily follow the order in which the contacts are represented in the instance.</t>
-  </si>
-  <si>
-    <t>ContactPoint.rank</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.period</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.period</t>
-  </si>
-  <si>
-    <t>Time period when the contact point was/is in use</t>
-  </si>
-  <si>
-    <t>Time period when the contact point was/is in use.</t>
-  </si>
-  <si>
-    <t>ContactPoint.period</t>
-  </si>
-  <si>
-    <t>./usablePeriod[type="IVL&lt;TS&gt;"]</t>
-  </si>
-  <si>
     <t>PractitionerRole.availableTime</t>
   </si>
   <si>
@@ -1684,6 +1431,9 @@
   </si>
   <si>
     <t>Indicates which days of the week are available between the start and end Times.</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>The days of the week.</t>
@@ -2109,10 +1859,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN91"/>
+  <dimension ref="A1:AN78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="70.05859375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="61.21484375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="46.96875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="36.3984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -4245,9 +3995,7 @@
       <c r="M19" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="N19" t="s" s="2">
-        <v>204</v>
-      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -4325,13 +4073,13 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>77</v>
@@ -4353,13 +4101,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4439,13 +4187,13 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>77</v>
@@ -4467,13 +4215,13 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4553,10 +4301,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4582,16 +4330,16 @@
         <v>111</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4640,7 +4388,7 @@
         <v>117</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4669,10 +4417,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4695,17 +4443,17 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4742,10 +4490,10 @@
         <v>77</v>
       </c>
       <c r="AB23" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AC23" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>77</v>
@@ -4754,7 +4502,7 @@
         <v>117</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4769,27 +4517,27 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AM23" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>230</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="C24" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>77</v>
@@ -4811,17 +4559,17 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4870,7 +4618,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4885,24 +4633,24 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AM24" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>230</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5011,10 +4759,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5125,10 +4873,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5154,16 +4902,16 @@
         <v>173</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -5188,31 +4936,31 @@
         <v>77</v>
       </c>
       <c r="X27" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="Y27" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="Y27" t="s" s="2">
+      <c r="Z27" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="Z27" t="s" s="2">
+      <c r="AA27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5230,7 +4978,7 @@
         <v>102</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -5241,10 +4989,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5267,19 +5015,19 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -5307,28 +5055,28 @@
         <v>153</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="Z28" t="s" s="2">
+      <c r="AA28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5343,10 +5091,10 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -5357,10 +5105,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5386,16 +5134,16 @@
         <v>137</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -5405,46 +5153,46 @@
         <v>77</v>
       </c>
       <c r="S29" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="T29" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="T29" t="s" s="2">
+      <c r="U29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5459,13 +5207,13 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AM29" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -5473,10 +5221,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5502,13 +5250,13 @@
         <v>104</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5522,43 +5270,43 @@
         <v>77</v>
       </c>
       <c r="T30" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5573,13 +5321,13 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -5587,10 +5335,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5613,16 +5361,16 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5672,7 +5420,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5684,16 +5432,16 @@
         <v>100</v>
       </c>
       <c r="AJ31" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AK31" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AK31" t="s" s="2">
+      <c r="AL31" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AM31" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5701,10 +5449,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5727,16 +5475,16 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5786,7 +5534,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5798,16 +5546,16 @@
         <v>100</v>
       </c>
       <c r="AJ32" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AK32" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AK32" t="s" s="2">
+      <c r="AL32" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AM32" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5815,13 +5563,13 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="C33" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>77</v>
@@ -5843,17 +5591,17 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5902,7 +5650,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5917,24 +5665,24 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>230</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6043,10 +5791,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6157,10 +5905,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6186,16 +5934,16 @@
         <v>173</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -6220,31 +5968,31 @@
         <v>77</v>
       </c>
       <c r="X36" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="Y36" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="Y36" t="s" s="2">
+      <c r="Z36" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="Z36" t="s" s="2">
+      <c r="AA36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF36" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6262,7 +6010,7 @@
         <v>102</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -6273,10 +6021,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6299,19 +6047,19 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6339,28 +6087,28 @@
         <v>153</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="Z37" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="Z37" t="s" s="2">
+      <c r="AA37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6375,10 +6123,10 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -6389,10 +6137,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6418,16 +6166,16 @@
         <v>137</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -6437,46 +6185,46 @@
         <v>77</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="T38" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="U38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6491,13 +6239,13 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -6505,10 +6253,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6534,13 +6282,13 @@
         <v>104</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6554,43 +6302,43 @@
         <v>77</v>
       </c>
       <c r="T39" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF39" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="U39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6605,13 +6353,13 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -6619,10 +6367,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6645,16 +6393,16 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6704,7 +6452,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6716,16 +6464,16 @@
         <v>100</v>
       </c>
       <c r="AJ40" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AK40" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AK40" t="s" s="2">
+      <c r="AL40" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -6733,10 +6481,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6759,16 +6507,16 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6818,7 +6566,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6830,16 +6578,16 @@
         <v>100</v>
       </c>
       <c r="AJ41" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AK41" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AK41" t="s" s="2">
+      <c r="AL41" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AM41" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -6847,10 +6595,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6873,26 +6621,26 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="O42" t="s" s="2">
+      <c r="P42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q42" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="P42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q42" t="s" s="2">
-        <v>322</v>
-      </c>
       <c r="R42" t="s" s="2">
         <v>77</v>
       </c>
@@ -6936,7 +6684,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6951,24 +6699,24 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AL42" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AL42" t="s" s="2">
+      <c r="AM42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>325</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6991,19 +6739,19 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="O43" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -7052,7 +6800,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7064,27 +6812,27 @@
         <v>100</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>333</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7193,10 +6941,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7307,10 +7055,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7333,16 +7081,16 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7392,7 +7140,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7401,16 +7149,16 @@
         <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -7421,10 +7169,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7447,68 +7195,68 @@
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q47" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="R47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF47" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="R47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7517,16 +7265,16 @@
         <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AL47" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -7537,10 +7285,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7563,16 +7311,16 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7622,7 +7370,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7634,13 +7382,13 @@
         <v>100</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -7651,10 +7399,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7677,16 +7425,16 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="M49" t="s" s="2">
-        <v>362</v>
-      </c>
       <c r="N49" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7736,7 +7484,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7748,13 +7496,13 @@
         <v>100</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -7765,10 +7513,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7791,19 +7539,19 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7831,16 +7579,16 @@
         <v>163</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="Z50" t="s" s="2">
+      <c r="AA50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB50" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
@@ -7850,7 +7598,7 @@
         <v>117</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7865,13 +7613,13 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL50" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM50" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -7879,13 +7627,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C51" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>77</v>
@@ -7907,19 +7655,19 @@
         <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="M51" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>77</v>
@@ -7944,11 +7692,11 @@
         <v>77</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
@@ -7966,7 +7714,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7981,13 +7729,13 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL51" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL51" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM51" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
@@ -7995,13 +7743,13 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C52" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>77</v>
@@ -8023,19 +7771,19 @@
         <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="M52" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -8060,11 +7808,11 @@
         <v>77</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>77</v>
@@ -8082,7 +7830,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8097,13 +7845,13 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL52" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL52" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM52" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
@@ -8111,13 +7859,13 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C53" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C53" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>77</v>
@@ -8139,19 +7887,19 @@
         <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="M53" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -8176,11 +7924,11 @@
         <v>77</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>77</v>
@@ -8198,7 +7946,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8213,13 +7961,13 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL53" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL53" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM53" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>77</v>
@@ -8227,13 +7975,13 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C54" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C54" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>77</v>
@@ -8255,19 +8003,19 @@
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="M54" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -8292,11 +8040,11 @@
         <v>77</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>77</v>
@@ -8314,7 +8062,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8329,13 +8077,13 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL54" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL54" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM54" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
@@ -8343,13 +8091,13 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C55" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C55" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>77</v>
@@ -8371,19 +8119,19 @@
         <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="M55" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -8408,11 +8156,11 @@
         <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -8430,7 +8178,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8445,13 +8193,13 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL55" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM55" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>
@@ -8459,13 +8207,13 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C56" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>77</v>
@@ -8487,19 +8235,19 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="M56" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -8524,11 +8272,11 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -8546,7 +8294,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8561,13 +8309,13 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL56" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL56" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM56" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
@@ -8575,13 +8323,13 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C57" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>77</v>
@@ -8603,19 +8351,19 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="M57" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8640,11 +8388,11 @@
         <v>77</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>77</v>
@@ -8662,7 +8410,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8677,13 +8425,13 @@
         <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL57" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL57" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM57" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>77</v>
@@ -8691,10 +8439,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8717,16 +8465,16 @@
         <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8755,11 +8503,11 @@
         <v>177</v>
       </c>
       <c r="Y58" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="Z58" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>407</v>
-      </c>
       <c r="AA58" t="s" s="2">
         <v>77</v>
       </c>
@@ -8776,7 +8524,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8791,13 +8539,13 @@
         <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AL58" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AL58" t="s" s="2">
+      <c r="AM58" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>77</v>
@@ -8805,10 +8553,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8831,16 +8579,16 @@
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>414</v>
-      </c>
       <c r="N59" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8890,7 +8638,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8902,27 +8650,27 @@
         <v>100</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>417</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8945,16 +8693,16 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="M60" t="s" s="2">
-        <v>421</v>
-      </c>
       <c r="N60" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9004,7 +8752,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9016,13 +8764,13 @@
         <v>100</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AL60" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
@@ -9033,10 +8781,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9059,17 +8807,17 @@
         <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -9106,7 +8854,7 @@
         <v>77</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AC61" s="2"/>
       <c r="AD61" t="s" s="2">
@@ -9116,7 +8864,7 @@
         <v>117</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9128,16 +8876,16 @@
         <v>100</v>
       </c>
       <c r="AJ61" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AK61" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AK61" t="s" s="2">
+      <c r="AL61" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AL61" t="s" s="2">
+      <c r="AM61" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>77</v>
@@ -9145,13 +8893,13 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C62" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C62" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>77</v>
@@ -9173,17 +8921,17 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -9232,7 +8980,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9244,16 +8992,16 @@
         <v>100</v>
       </c>
       <c r="AJ62" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AK62" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AK62" t="s" s="2">
-        <v>431</v>
-      </c>
       <c r="AL62" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>77</v>
@@ -9261,10 +9009,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9275,10 +9023,10 @@
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>77</v>
@@ -9287,15 +9035,17 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>104</v>
+        <v>440</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>105</v>
+        <v>441</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>443</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9344,25 +9094,25 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>107</v>
+        <v>439</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>108</v>
+        <v>444</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
@@ -9373,21 +9123,21 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>77</v>
@@ -9399,17 +9149,15 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>77</v>
@@ -9446,37 +9194,37 @@
         <v>77</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
@@ -9487,23 +9235,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>445</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>77</v>
@@ -9515,15 +9261,17 @@
         <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>446</v>
+        <v>111</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>447</v>
+        <v>112</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -9560,16 +9308,16 @@
         <v>77</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF65" t="s" s="2">
         <v>118</v>
@@ -9601,42 +9349,46 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>77</v>
+        <v>448</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>105</v>
+        <v>449</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>77</v>
       </c>
@@ -9684,25 +9436,25 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>107</v>
+        <v>451</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
@@ -9713,7 +9465,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>452</v>
@@ -9727,7 +9479,7 @@
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>77</v>
@@ -9739,7 +9491,7 @@
         <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>111</v>
+        <v>173</v>
       </c>
       <c r="L67" t="s" s="2">
         <v>453</v>
@@ -9747,7 +9499,9 @@
       <c r="M67" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="N67" s="2"/>
+      <c r="N67" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>77</v>
@@ -9772,31 +9526,31 @@
         <v>77</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>77</v>
+        <v>243</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>77</v>
+        <v>456</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>77</v>
+        <v>457</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>118</v>
+        <v>452</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9808,13 +9562,13 @@
         <v>100</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>77</v>
+        <v>444</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
@@ -9825,10 +9579,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9836,7 +9590,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>88</v>
@@ -9851,24 +9605,22 @@
         <v>77</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>137</v>
+        <v>316</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>459</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" t="s" s="2">
-        <v>460</v>
+        <v>77</v>
       </c>
       <c r="S68" t="s" s="2">
         <v>77</v>
@@ -9910,25 +9662,25 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>102</v>
+        <v>444</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
@@ -9939,10 +9691,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9965,15 +9717,17 @@
         <v>77</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>149</v>
+        <v>462</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>77</v>
@@ -9983,7 +9737,7 @@
         <v>77</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>466</v>
+        <v>77</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>77</v>
@@ -9998,11 +9752,13 @@
         <v>77</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y69" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z69" t="s" s="2">
-        <v>467</v>
+        <v>77</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>77</v>
@@ -10020,7 +9776,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10038,7 +9794,7 @@
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>102</v>
+        <v>444</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>77</v>
@@ -10049,14 +9805,12 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="C70" t="s" s="2">
-        <v>470</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
         <v>77</v>
       </c>
@@ -10068,7 +9822,7 @@
         <v>88</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>77</v>
@@ -10077,15 +9831,17 @@
         <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>468</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -10134,25 +9890,25 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>118</v>
+        <v>466</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>77</v>
+        <v>444</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
@@ -10163,10 +9919,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10174,32 +9930,30 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>173</v>
+        <v>440</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>478</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -10209,7 +9963,7 @@
         <v>77</v>
       </c>
       <c r="S71" t="s" s="2">
-        <v>479</v>
+        <v>77</v>
       </c>
       <c r="T71" t="s" s="2">
         <v>77</v>
@@ -10224,13 +9978,13 @@
         <v>77</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>244</v>
+        <v>77</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>480</v>
+        <v>77</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>481</v>
+        <v>77</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>77</v>
@@ -10248,28 +10002,28 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>482</v>
+        <v>469</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>483</v>
+        <v>100</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>484</v>
+        <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>485</v>
+        <v>444</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>486</v>
+        <v>77</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>77</v>
@@ -10277,10 +10031,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>488</v>
+        <v>472</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10288,35 +10042,31 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K72" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>489</v>
+        <v>105</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>492</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>77</v>
       </c>
@@ -10364,7 +10114,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>493</v>
+        <v>107</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10373,19 +10123,19 @@
         <v>88</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>494</v>
+        <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>495</v>
+        <v>108</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>281</v>
+        <v>77</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>77</v>
@@ -10393,46 +10143,44 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>496</v>
+        <v>473</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>497</v>
+        <v>473</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>173</v>
+        <v>111</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>498</v>
+        <v>112</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>499</v>
+        <v>113</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>501</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>77</v>
       </c>
@@ -10456,52 +10204,52 @@
         <v>77</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>244</v>
+        <v>77</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>502</v>
+        <v>77</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>503</v>
+        <v>77</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>504</v>
+        <v>118</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>505</v>
+        <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>506</v>
+        <v>102</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>507</v>
+        <v>77</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>77</v>
@@ -10509,44 +10257,46 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>508</v>
+        <v>474</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>509</v>
+        <v>474</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>77</v>
+        <v>448</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J74" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>510</v>
+        <v>111</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>511</v>
+        <v>449</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>512</v>
+        <v>450</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="O74" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>77</v>
       </c>
@@ -10594,25 +10344,25 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>514</v>
+        <v>451</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -10623,10 +10373,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>515</v>
+        <v>475</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>516</v>
+        <v>475</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10634,7 +10384,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>88</v>
@@ -10646,19 +10396,19 @@
         <v>77</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>284</v>
+        <v>104</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>517</v>
+        <v>476</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>518</v>
+        <v>477</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>287</v>
+        <v>455</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10708,10 +10458,10 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>519</v>
+        <v>475</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>88</v>
@@ -10720,16 +10470,16 @@
         <v>100</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>289</v>
+        <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>520</v>
+        <v>108</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>292</v>
+        <v>77</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>77</v>
@@ -10737,10 +10487,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>521</v>
+        <v>478</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>521</v>
+        <v>478</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10751,10 +10501,10 @@
         <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>77</v>
@@ -10763,16 +10513,16 @@
         <v>77</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>522</v>
+        <v>283</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>523</v>
+        <v>479</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>524</v>
+        <v>480</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>525</v>
+        <v>286</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10822,25 +10572,25 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>521</v>
+        <v>478</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>101</v>
+        <v>288</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>77</v>
+        <v>481</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>526</v>
+        <v>444</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
@@ -10851,10 +10601,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>527</v>
+        <v>482</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>527</v>
+        <v>482</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10865,10 +10615,10 @@
         <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>77</v>
@@ -10880,12 +10630,14 @@
         <v>104</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>105</v>
+        <v>483</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>484</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>77</v>
@@ -10934,7 +10686,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>107</v>
+        <v>482</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10943,16 +10695,16 @@
         <v>88</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>108</v>
+        <v>444</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>77</v>
@@ -10963,24 +10715,24 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>528</v>
+        <v>485</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>528</v>
+        <v>485</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>77</v>
@@ -10989,18 +10741,20 @@
         <v>77</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>111</v>
+        <v>486</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>112</v>
+        <v>487</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>113</v>
+        <v>488</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O78" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>77</v>
       </c>
@@ -11036,19 +10790,19 @@
         <v>77</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>118</v>
+        <v>485</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11060,1505 +10814,23 @@
         <v>100</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>119</v>
+        <v>299</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>102</v>
+        <v>490</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="79" hidden="true">
-      <c r="A79" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="P79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q79" s="2"/>
-      <c r="R79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="80" hidden="true">
-      <c r="A80" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="O80" s="2"/>
-      <c r="P80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="81" hidden="true">
-      <c r="A81" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
-      <c r="P81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="82" hidden="true">
-      <c r="A82" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="O82" s="2"/>
-      <c r="P82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="83" hidden="true">
-      <c r="A83" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="O83" s="2"/>
-      <c r="P83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="84" hidden="true">
-      <c r="A84" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E84" s="2"/>
-      <c r="F84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
-      <c r="P84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q84" s="2"/>
-      <c r="R84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="85" hidden="true">
-      <c r="A85" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="C85" s="2"/>
-      <c r="D85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E85" s="2"/>
-      <c r="F85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G85" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K85" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L85" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
-      <c r="P85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q85" s="2"/>
-      <c r="R85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AG85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH85" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="86" hidden="true">
-      <c r="A86" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="C86" s="2"/>
-      <c r="D86" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="E86" s="2"/>
-      <c r="F86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K86" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L86" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O86" s="2"/>
-      <c r="P86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q86" s="2"/>
-      <c r="R86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI86" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ86" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL86" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="87" hidden="true">
-      <c r="A87" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="C87" s="2"/>
-      <c r="D87" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="E87" s="2"/>
-      <c r="F87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K87" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L87" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="P87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q87" s="2"/>
-      <c r="R87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="AG87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI87" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ87" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL87" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="88" hidden="true">
-      <c r="A88" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="C88" s="2"/>
-      <c r="D88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E88" s="2"/>
-      <c r="F88" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G88" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K88" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L88" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="O88" s="2"/>
-      <c r="P88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q88" s="2"/>
-      <c r="R88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="AG88" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH88" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI88" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ88" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="89" hidden="true">
-      <c r="A89" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="C89" s="2"/>
-      <c r="D89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E89" s="2"/>
-      <c r="F89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G89" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K89" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="L89" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O89" s="2"/>
-      <c r="P89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q89" s="2"/>
-      <c r="R89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="AG89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="90" hidden="true">
-      <c r="A90" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="C90" s="2"/>
-      <c r="D90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E90" s="2"/>
-      <c r="F90" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G90" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H90" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="I90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K90" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="O90" s="2"/>
-      <c r="P90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q90" s="2"/>
-      <c r="R90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="AG90" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI90" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ90" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="AM90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="91" hidden="true">
-      <c r="A91" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="C91" s="2"/>
-      <c r="D91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E91" s="2"/>
-      <c r="F91" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G91" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H91" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="I91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K91" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="L91" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="P91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q91" s="2"/>
-      <c r="R91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="AG91" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI91" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ91" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AK91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN91" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN91">
+  <autoFilter ref="A1:AN78">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12568,7 +10840,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI90">
+  <conditionalFormatting sqref="A2:AI77">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nr-update-valueset/ig/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/nr-update-valueset/ig/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-07T12:17:43+00:00</t>
+    <t>2024-03-07T12:27:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
